--- a/Results/rbf_fd_parameter_study_9.xlsx
+++ b/Results/rbf_fd_parameter_study_9.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1053,6 +1053,721 @@
         <v>250</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>178.2112961597919</v>
+      </c>
+      <c r="L12" t="n">
+        <v>67.69477777128331</v>
+      </c>
+      <c r="M12" t="n">
+        <v>36.26657500878832</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.03502470257662597</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.007469519897290423</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>115.8985805716706</v>
+      </c>
+      <c r="L13" t="n">
+        <v>38.0754590950819</v>
+      </c>
+      <c r="M13" t="n">
+        <v>19.28220762172236</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.03320160255272039</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.007173404661602578</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0007591084855119141</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0002328382235078031</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0003699912936320866</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.001642786086030613</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0007426447111531608</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.403657147239615e-05</v>
+      </c>
+      <c r="L15" t="n">
+        <v>4.983293196371654e-06</v>
+      </c>
+      <c r="M15" t="n">
+        <v>7.737613971913157e-06</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.0001051034882348587</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.709424990551273e-05</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>100</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>100</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.007965229288399314</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.002482350464753719</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.00344545515418021</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.001506549559452038</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.0004567547186527068</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>100</v>
+      </c>
+      <c r="B17" t="n">
+        <v>100</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>100</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H17" t="n">
+        <v>12</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.0002188499026384287</v>
+      </c>
+      <c r="L17" t="n">
+        <v>8.519888728885538e-05</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.0002610649795615952</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.0004123909184769904</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.0001806504073554363</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>100</v>
+      </c>
+      <c r="B18" t="n">
+        <v>100</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>100</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H18" t="n">
+        <v>12</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.0001286263726818068</v>
+      </c>
+      <c r="L18" t="n">
+        <v>4.892142589374977e-05</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.0001558903359243233</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.001420446950893599</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.0006222107062757443</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>100</v>
+      </c>
+      <c r="B19" t="n">
+        <v>100</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H19" t="n">
+        <v>12</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.000165721402776187</v>
+      </c>
+      <c r="L19" t="n">
+        <v>7.061645624524534e-05</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.0001545508238230177</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.001627546189844785</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.001334162986937797</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>100</v>
+      </c>
+      <c r="B20" t="n">
+        <v>100</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>100</v>
+      </c>
+      <c r="E20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H20" t="n">
+        <v>12</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.0001945336168206927</v>
+      </c>
+      <c r="L20" t="n">
+        <v>5.121242916613838e-05</v>
+      </c>
+      <c r="M20" t="n">
+        <v>8.858382271675916e-05</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.000256635029209935</v>
+      </c>
+      <c r="O20" t="n">
+        <v>6.454993685705845e-05</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>100</v>
+      </c>
+      <c r="B21" t="n">
+        <v>100</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>100</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H21" t="n">
+        <v>12</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.0001867753368067469</v>
+      </c>
+      <c r="L21" t="n">
+        <v>5.102329716455318e-05</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.0002065006528679186</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.0009094408703759476</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.0002444020006412125</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>100</v>
+      </c>
+      <c r="B22" t="n">
+        <v>100</v>
+      </c>
+      <c r="C22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>100</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H22" t="n">
+        <v>12</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.0004020978899127654</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.0001359155354183319</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.0008455887028041009</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.003167924358886785</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.002607860957958509</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>100</v>
+      </c>
+      <c r="B23" t="n">
+        <v>100</v>
+      </c>
+      <c r="C23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E23" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H23" t="n">
+        <v>12</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.0003386612124843653</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.0001066967763003635</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.001682504551076015</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.00714411565931504</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.001126262332378007</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>100</v>
+      </c>
+      <c r="B24" t="n">
+        <v>100</v>
+      </c>
+      <c r="C24" t="n">
+        <v>15</v>
+      </c>
+      <c r="D24" t="n">
+        <v>100</v>
+      </c>
+      <c r="E24" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H24" t="n">
+        <v>12</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.003578935470417626</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.0002504945971354036</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.04889314359604216</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.427069551204194</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.05685387923234689</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Results/rbf_fd_parameter_study_9.xlsx
+++ b/Results/rbf_fd_parameter_study_9.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1771,4 +1772,765 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.002726854521259436</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0003240318930495527</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0009103189991348941</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.006041600621319617</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.001287033964474454</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.061475538194885e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>6.736746297899761e-06</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.976589887204795e-05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0008738274670142342</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0001913438382225976</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.000264117177322943</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0001024966760512011</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0002276891733529457</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.002408545613247136</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0007665637863504012</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0001847922942483814</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5.926143874824262e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0002336933809742935</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.002504065801275262</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0005191841979960845</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8.359704468182686e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.412721269515232e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6.569715114379368e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.0004483633963922114</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0002389214580363619</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.333167886691807e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.409259866804516e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.7778480140462e-05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0006937862386330806</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.000342393138178646</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0001313154433234909</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3.870551326993025e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0001101166940169964</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0008287918985630951</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0004410083291350326</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001286263726818068</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4.892142589374977e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0001558903359243233</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.001420446950893599</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0006222107062757443</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>115</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0001541345408261475</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.746094965959776e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0001367755807466846</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.001119632475481417</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0007577623899409826</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>130</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0004453841203159999</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0001557038811816547</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0002985322094188564</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.001179753491831767</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0008859807021506402</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>150</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.001831459513083753</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0007233112772040551</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.0012614298337916</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.001699997313666075</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0009617089426057849</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>200</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.006976665165703e-05</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.314862346204705e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.837875531671207e-05</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.0004599290105728923</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.000116862669711763</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_9.xlsx
+++ b/Results/rbf_fd_parameter_study_9.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -3176,4 +3177,820 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0005185688950076222</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0005284672855223279</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0006238227449680002</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.01282916281593303</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.007883195500917475</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0004758754653849725</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.000206533313048243</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.000459529700692027</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.006630714458062747</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.004202947855864641</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.000234652405235752</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0001183815729483849</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0001989547728696887</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.001686461322120933</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.001289891384136624</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0006421867676250849</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0002048040026941632</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0004887860632242785</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.001288138857876465</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0009421473983611285</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6.278283083152289e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3.097174222345815e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>9.068975893069974e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.001395060302992411</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0006800953974225586</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0001115256848218405</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4.781038470526185e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0001610304170001998</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.001408419688693054</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0006493306179016638</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7.927558165423369e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3.052958015323699e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>8.921498433630874e-05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.00141911676602667</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0006251950869541789</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001286263726818068</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4.892142589374977e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0001558903359243233</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.001420446950893599</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0006222107062757443</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0001348753619793319</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.058827991155909e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0001695140121432599</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.001421516575071099</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0006198285941502793</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0001440075704676095</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.436999879354613e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0001784109903591652</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.001421649316260802</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0006195311718330279</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0001581026038840504</v>
+      </c>
+      <c r="L12" t="n">
+        <v>5.976661061685599e-05</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.0001914532273749497</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.001421756776131256</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0006192932917958989</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0001617641690181414</v>
+      </c>
+      <c r="L13" t="n">
+        <v>6.069375949062169e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0001937059090718161</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.001421766586736863</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.0006192635074567929</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>5e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0001647605265649925</v>
+      </c>
+      <c r="L14" t="n">
+        <v>6.148618299365867e-05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0001956364607039635</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.001421783192984072</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0006192397920793977</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>1e-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_9.xlsx
+++ b/Results/rbf_fd_parameter_study_9.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Eigenvector Angle" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -3993,4 +3994,600 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.39951525765996</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.9686907334880267</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.6934554471549287</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.6226630558003</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.2207648657039704</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0001853422823447267</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0001078478351207327</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0002148718128870415</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.001721222029769144</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0007810483925738753</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.001894997496808628</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.000505328334438854</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.001013591240378281</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.001165577708036249</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0006563968896698639</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>9.853158307172639e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.932488484280425e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>7.303129768343462e-05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.001061368680639095</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0006204581358751606</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0001286263726818068</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4.892142589374977e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0001558903359243233</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.001420446950893599</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0006222107062757443</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>8.5819114290313e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.858553433884513e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6.266898345100923e-05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0010602806058258</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0006212155284294046</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.000184356147256868</v>
+      </c>
+      <c r="L8" t="n">
+        <v>6.817834711697526e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0001483371015276009</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.001165578236621723</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0006571962970073257</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0002221900469939562</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001293213678740155</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.00022659657641141</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.001721222123488192</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0007816434305104307</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.39963930260562</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.9687930799395449</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.6935191725306855</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.622663089861437</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.22076486124879</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_9.xlsx
+++ b/Results/rbf_fd_parameter_study_9.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1056,4 +1057,930 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.004969308799203196</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.001924669134515011</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.003079819785426128</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.01241366213256168</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.003139979420631388</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.004708176183057001</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.001833441981102935</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.002932509064660757</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.01176494861123683</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.003049600323311434</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>8.934196347070381e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3.724391127656288e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>9.213452934200291e-05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0002542670755506239</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0002386776485597966</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0006863916096624105</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0003118544162083701</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0007713618497982048</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.0001125401019225061</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0001105581474902003</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.100779257060234e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6.769164042731361e-06</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.595625917623387e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.0003191619994698886</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5.579130051058282e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.583574835569723e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.528166762950035e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.564658643949922e-05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.000780705771677617</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0001380120038438495</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.71207171034906e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.23577324675642e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.130755463397212e-05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.001796687547826065</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0002894565926733786</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7.322451090300088e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.345588206370972e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>8.834412400621055e-05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.001579863878887857</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0003697324228920691</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.925712737087437e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.069197143303951e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.204775664715543e-05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.00316691310900492</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0007079042961017135</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.000101657077478876</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.839493285326695e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0001636879091367928</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.003290922245281238</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.001369514384094212</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.050383719205283e-05</v>
+      </c>
+      <c r="L12" t="n">
+        <v>5.073923454656312e-06</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.0001596979046551251</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.02702465021326167</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.002539531173392633</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>30</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0001908872474793055</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.760530396886561e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.001742607121290805</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.4287680862287203</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.01309424747795591</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.002525124827626278</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0002970498793998122</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0832516291392561</v>
+      </c>
+      <c r="N14" t="n">
+        <v>9.72330122277871</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.2892004002234682</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" t="n">
+        <v>30</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.001901310865880378</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.0008793966368091341</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.0205856760859323</v>
+      </c>
+      <c r="N15" t="n">
+        <v>63.09866464941121</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.945558586834207</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>100</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" t="n">
+        <v>30</v>
+      </c>
+      <c r="E16" t="n">
+        <v>12</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.02067571887956877</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.02311985541622628</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.09458679371305299</v>
+      </c>
+      <c r="N16" t="n">
+        <v>92.65556440456845</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5.374597539775221</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_9.xlsx
+++ b/Results/rbf_fd_parameter_study_9.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1983,4 +1984,875 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.07565630715561276</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.006617557860764647</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.02273022404513934</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.02450463247268863</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.004347217267984075</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0002070783113084268</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3.425956227441904e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0002832316918710223</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.003266370699194235</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0006413398072421136</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0001343639276108079</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5.755009431838413e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0001733949955002563</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0009784502184280904</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0005038820672569921</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>9.296994141562049e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3.74682201615982e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>8.661308566486749e-05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.001671787356673791</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0009597659606257224</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.001337712366278192</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0003904840592269546</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.001297135491861807</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.002257304324646623</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.001444110955406088</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0002732664953917394</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0001152404047588506</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0002649997516347492</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.002767470252210688</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.001908743372811055</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0002570957511704754</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0001204126625837079</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0003246064923238334</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.002985942929945578</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.002489431957200003</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0003419459522694258</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9.695157867721978e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0007211569764965094</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.001362135813533065</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0002784398764150153</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>115</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0007390710615032221</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0001862070887588457</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0007288543282443881</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.000413762224720102</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0001054926316330059</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>130</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>7.573585278640722e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.981688732678235e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>7.048247131698676e-05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0007856838037030417</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.000129195192715797</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>150</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0003613692848479644</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0001059497008088355</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.0002084778362520439</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.0008235617028025477</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0002402701508859436</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>175</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0002191631210283472</v>
+      </c>
+      <c r="L13" t="n">
+        <v>8.337259165256512e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0001646234370997469</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.0006578884954922095</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.0001878330094032729</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>200</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0007470620966024877</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0002429159848983948</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0004642308317606699</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.0006353333389795719</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0002909440595227554</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>250</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.000630478457486588</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.0002169884682198029</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.0003149194729188993</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.001048883547992639</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.0003401396191345085</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_9.xlsx
+++ b/Results/rbf_fd_parameter_study_9.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2855,4 +2856,655 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.708974112045415e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.117272171677085e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.71172039987422e-05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.001526029422562548</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0004272684351635097</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.320728846329369e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.102310277681616e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.470395949291163e-05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.001510341752124185</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0004248485076381107</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.494629935348464e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.127045044605028e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.185698938959314e-05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.001513727301011357</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0004234244387343655</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.315362593537411e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.109505338733266e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.686169777020134e-05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.0014949055211937</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0004223663527259153</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.321987401043418e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.108939304402634e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.651049163996243e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.001492620058810668</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0004220242515186554</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6.023942616345867e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.45467579730828e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>9.096588829224374e-05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.003167145855349686</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0007083429594058789</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.224676722786255e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.330124950030083e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>7.675178329970941e-05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.003165062205176082</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0007077913455342632</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.925712737087437e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.069197143303951e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.204775664715543e-05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.00316691310900492</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0007079042961017135</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0001751936105092066</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4.629901693236086e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0003188034637073025</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.003166204377016117</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0007169830531127338</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.189386657292068e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.304836355029794e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4.637607599740563e-05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.003165248151408909</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.000711149401649016</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_9.xlsx
+++ b/Results/rbf_fd_parameter_study_9.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3507,4 +3508,820 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0001360874698073868</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0001459619218333348</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0002965297214774783</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.01383019903623072</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.003840293456824104</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>7.908457628346549e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>7.505383981914145e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0001495866280395689</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.006923853704553834</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.00202688495703223</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.860058309037946e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.627630210573466e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>5.868460596810259e-05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.002858257332526634</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0008123369280309125</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.119000778989392e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.762488791610437e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>7.986204309352245e-05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.003013360956487537</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.000738444706094928</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.55584605460176e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.288248252500864e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6.369112253908592e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.003137443487298614</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0007101136098307558</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.220421260279008e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.330380184815083e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>7.016649235832365e-05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.003152953772013787</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0007087284698296493</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0001623310143068695</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3.482256033743054e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0002618472907527894</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.003165362000779207</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0007079760618308492</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.925712737087437e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.069197143303951e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.204775664715543e-05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.00316691310900492</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0007079042961017135</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.200028361307885e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.685490305848603e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0001058997181264276</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.003168153891070206</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0007078504587403305</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.977715565455532e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.583464582041245e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>8.92872874816915e-05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.003168308990631646</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0007078439671414106</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.253145476096599e-05</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.604465394423365e-05</v>
+      </c>
+      <c r="M12" t="n">
+        <v>8.591212444410457e-05</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.003168433084163089</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0007078387858750662</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>30</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.311890348508851e-05</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.617435251711671e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>8.621184610095073e-05</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.003168448611162682</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.0007078381450197943</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>5e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.36467280104052e-05</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.629736396945778e-05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>8.656759578007861e-05</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.003168461015277449</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0007078376355089748</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>1e-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_9.xlsx
+++ b/Results/rbf_fd_parameter_study_9.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Eigenvector Angle" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4324,4 +4325,600 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.07855070804235183</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.05128112798871489</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.04035751100912018</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.04903373759292407</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.02065218821923874</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.694296303173294e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3.91728103739445e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0001099899652265325</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.002489535662541714</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0004231509585286001</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0009199543189015336</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0004708886030554343</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0009833344732990902</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.001995262235585943</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.000420868643788594</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0001014537330092252</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.869200397230136e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.000115650783606378</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.002511002324694368</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0005429391731930619</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.925712737087437e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.069197143303951e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.204775664715543e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.00316691310900492</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0007079042961017135</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5.536339274015257e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.481295691243953e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0001155558889375054</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.002471333505368975</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.000542001490220447</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0002518063282932723</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8.979736829319733e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0003824438376407637</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.002552765395147995</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0004200389574053397</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0004815264492391937</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0002099168540617566</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0004665083406693165</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.002841662895123668</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0004229999706155998</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.07855081967123026</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.05128119734863372</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.04035756668752474</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.04903373574744297</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.02065218833127289</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>